--- a/site/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Manage Cost Centers</t>
+          <t>Application Configurations</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -683,29 +683,29 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cost Center Settings</t>
+          <t>Worker Sync Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+          <t>h_01KRGAQHMKDXHEHE5NM9ZCVBZ5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KRGAQHMKDXHEHE5NM9ZCVBZ5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>Cost Center Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KQVMYBGQVNVAWK8JY6JC9VHE</t>
+          <t>h_01KGMG4JM39E5ES9AGZFATM7WD</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KQVMYBGQVNVAWK8JY6JC9VHE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KGMG4JM39E5ES9AGZFATM7WD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Provisioning Settings</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
+          <t>h_01KQVMYBGQVNVAWK8JY6JC9VHE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KQVMYBGQVNVAWK8JY6JC9VHE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Provisioning Threshold</t>
+          <t>Provisioning Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,41 +759,41 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
+          <t>h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sensitive Fields</t>
+          <t>Provisioning Threshold</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Sensitive Fields</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,41 +847,41 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Success Notifications</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Failure Notifications</t>
+          <t>Success Notifications</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,19 +913,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Failure Notifications</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,41 +935,41 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,98 +979,120 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Source Filter</t>
+          <t>Debug Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KMMWQQRF8166YPHRS870BX9H</t>
+          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMMWQQRF8166YPHRS870BX9H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Source Filter</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KMMWQQRF8166YPHRS870BX9H</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMMWQQRF8166YPHRS870BX9H</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,19 +693,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KRGAQHMKDXHEHE5NM9ZCVBZ5</t>
+          <t>h_01KRGHYGXSHZGM7MVSB83V5APW</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KRGAQHMKDXHEHE5NM9ZCVBZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KRGHYGXSHZGM7MVSB83V5APW</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cost Center Settings</t>
+          <t>User Match Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>Source Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KQVMYBGQVNVAWK8JY6JC9VHE</t>
+          <t>h_01KRGC3NR44QDZHD20J29AB4N8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KQVMYBGQVNVAWK8JY6JC9VHE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KRGC3NR44QDZHD20J29AB4N8</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Provisioning Threshold</t>
+          <t>Execution Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sensitive Fields</t>
+          <t>Debug Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,41 +803,41 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Source Filter</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>h_01KMMWQQRF8166YPHRS870BX9H</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMMWQQRF8166YPHRS870BX9H</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,41 +869,41 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Success Notifications</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,19 +913,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMDB9FBA9XQX58JJ5R0BJGRS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Failure Notifications</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>h_01KRGHYGXSD8NWDN7EKG9G42WZ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMYRKV8WABFW2SDY1JHBDHCX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KRGHYGXSD8NWDN7EKG9G42WZ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Success Notification Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>h_01KRGHYGXSV2916CB2H9D2CMPX</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMF2X3G32JK6ZPBW74RWAJ7K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KRGHYGXSV2916CB2H9D2CMPX</t>
         </is>
       </c>
     </row>
@@ -991,108 +991,64 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Source Filter</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KMMWQQRF8166YPHRS870BX9H</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMMWQQRF8166YPHRS870BX9H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Execute Integration</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>General Settings</t>
+          <t>Execution Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -661,29 +661,29 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Application Configurations</t>
+          <t>General Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+          <t>h_01KVTDMRJY9SCYKSMT8V1383Y5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KVTDMRJY9SCYKSMT8V1383Y5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Worker Sync Settings</t>
+          <t>Application Configurations</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,41 +693,41 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KRGHYGXSHZGM7MVSB83V5APW</t>
+          <t>h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KRGHYGXSHZGM7MVSB83V5APW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>User Match Settings</t>
+          <t>User Sync Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+          <t>h_01KRGHYGXSHZGM7MVSB83V5APW</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KRGHYGXSHZGM7MVSB83V5APW</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Source Settings</t>
+          <t>User Match Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KRGC3NR44QDZHD20J29AB4N8</t>
+          <t>h_01KGMG4JM39E5ES9AGZFATM7WD</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KRGC3NR44QDZHD20J29AB4N8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KGMG4JM39E5ES9AGZFATM7WD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Provisioning Settings</t>
+          <t>Source Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
+          <t>h_01KRGC3NR44QDZHD20J29AB4N8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KRGC3NR44QDZHD20J29AB4N8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Execution Settings</t>
+          <t>Target Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,41 +781,41 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
+          <t>h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMMM7K00V0ETTP6KJQ26Y8DW</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>Safeguard Limits</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMMMGEBSKPCF8YW78AQ9HEVX</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Source Filter</t>
+          <t>Provisioning Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,107 +825,107 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KMMWQQRF8166YPHRS870BX9H</t>
+          <t>h_01KVTDMRJYFNACZ5FF2YVQZXP9</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMMWQQRF8166YPHRS870BX9H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KVTDMRJYFNACZ5FF2YVQZXP9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Create Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>h_01KVTC953BPSTJTPK18TWQFWTX</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KVTC953BPSTJTPK18TWQFWTX</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Update Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01KVTDMRJY8Y9645E5NVNND6QN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KVTDMRJY8Y9645E5NVNND6QN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Terminate Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01KVTDMRJYZS6F2QG55GQRDVRW</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KVTDMRJYZS6F2QG55GQRDVRW</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Debug Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Source Filter</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,41 +935,41 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KRGHYGXSD8NWDN7EKG9G42WZ</t>
+          <t>h_01KMMWQQRF8166YPHRS870BX9H</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KRGHYGXSD8NWDN7EKG9G42WZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMMWQQRF8166YPHRS870BX9H</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Success Notification Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KRGHYGXSV2916CB2H9D2CMPX</t>
+          <t>h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KRGHYGXSV2916CB2H9D2CMPX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMMWWZASCF14V76882FQNPZ5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,76 +979,186 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Notification Template Settings</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01KRGHYGXSD8NWDN7EKG9G42WZ</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KRGHYGXSD8NWDN7EKG9G42WZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Success Notification Settings</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01KRGHYGXSV2916CB2H9D2CMPX</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KRGHYGXSV2916CB2H9D2CMPX</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Log Insights</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1079,86 +1079,152 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Failure Notification Settings</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KW9EKY0EY3J1BY48W67FKYKZ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KW9EKY0EY3J1BY48W67FKYKZ</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>User Sync Transaction Failure Notification Settings</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KW9EKY0ES28NFAQN47RR8RPJ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KW9EKY0ES28NFAQN47RR8RPJ</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>h_01KW9EKY0E4316ZPDYJJSE2PJ2</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01KW9EKY0E4316ZPDYJJSE2PJ2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-Viewpoint-Spectrum-Integration-Guide/headings.xlsx
@@ -1123,7 +1123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Insights</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
